--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487710_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487710_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1646</v>
+        <v>12.565</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0914</v>
+        <v>11.4918</v>
       </c>
       <c r="F2" t="n">
         <v>1.0732</v>
@@ -610,10 +610,10 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1047</v>
+        <v>-0.7043</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9085</v>
+        <v>-0.5081</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1962</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6427</v>
+        <v>6.4534</v>
       </c>
       <c r="E3" t="n">
-        <v>3.034</v>
+        <v>4.7948</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6087</v>
+        <v>1.6585</v>
       </c>
       <c r="G3" t="n">
-        <v>3.321</v>
+        <v>4.9168</v>
       </c>
       <c r="H3" t="n">
-        <v>1.586</v>
+        <v>-0.8601</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7351</v>
+        <v>5.777</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6377</v>
+        <v>5.3422</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2317</v>
+        <v>0.0824</v>
       </c>
       <c r="L3" t="n">
-        <v>0.406</v>
+        <v>5.2598</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6833</v>
+        <v>-0.4254</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3542</v>
+        <v>-0.9425</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3291</v>
+        <v>0.5172</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5455</v>
+        <v>-0.2978</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3963</v>
+        <v>-0.8294</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1492</v>
+        <v>0.5317</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5802</v>
+        <v>5.8368</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5946</v>
+        <v>3.5247</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9856</v>
+        <v>2.3122</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9168</v>
+        <v>4.6101</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8601</v>
+        <v>0.318</v>
       </c>
       <c r="I4" t="n">
-        <v>5.777</v>
+        <v>4.2921</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3422</v>
+        <v>3.2547</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0824</v>
+        <v>0.0247</v>
       </c>
       <c r="L4" t="n">
-        <v>5.2598</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4254</v>
+        <v>1.3554</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9425</v>
+        <v>0.2933</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5172</v>
+        <v>1.0622</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1709</v>
+        <v>-0.6673</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0296</v>
+        <v>-0.2658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8587</v>
+        <v>-0.4015</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2184</v>
+        <v>5.0421</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1243</v>
+        <v>2.033</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0941</v>
+        <v>3.0091</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6101</v>
+        <v>3.321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.318</v>
+        <v>1.586</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2921</v>
+        <v>1.7351</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2547</v>
+        <v>1.6377</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0247</v>
+        <v>1.2317</v>
       </c>
       <c r="L5" t="n">
-        <v>3.23</v>
+        <v>0.406</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3554</v>
+        <v>1.6833</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2933</v>
+        <v>0.3542</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0622</v>
+        <v>1.3291</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2858</v>
+        <v>0.9449</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6662</v>
+        <v>0.3953</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.5496</v>
       </c>
       <c r="V5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ RIVERO</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4698</v>
+        <v>2.7365</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4347</v>
+        <v>0.412</v>
       </c>
       <c r="F6" t="n">
-        <v>1.035</v>
+        <v>2.3245</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6169</v>
+        <v>2.9642</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2894</v>
+        <v>-0.7423</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9063</v>
+        <v>3.7065</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2598</v>
+        <v>1.6872</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0041</v>
+        <v>-0.2842</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2556</v>
+        <v>1.9715</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6429</v>
+        <v>1.277</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2935</v>
+        <v>-0.4581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6506</v>
+        <v>1.7351</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2366</v>
+        <v>-0.7038</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3623</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1256</v>
+        <v>-0.1166</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4477</v>
+        <v>0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4477</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>P. RODRIGUEZ RIVERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2638</v>
+        <v>2.3057</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2118</v>
+        <v>1.1344</v>
       </c>
       <c r="F7" t="n">
-        <v>2.052</v>
+        <v>1.1713</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9642</v>
+        <v>1.6169</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7423</v>
+        <v>-1.2894</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7065</v>
+        <v>2.9063</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6872</v>
+        <v>2.2598</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2842</v>
+        <v>0.0041</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9715</v>
+        <v>2.2556</v>
       </c>
       <c r="M7" t="n">
-        <v>1.277</v>
+        <v>-0.6429</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4581</v>
+        <v>-1.2935</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7351</v>
+        <v>0.6506</v>
       </c>
       <c r="P7" t="n">
-        <v>0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1765</v>
+        <v>-0.4007</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7874</v>
+        <v>-0.6626</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3892</v>
+        <v>0.2619</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2821</v>
+        <v>2.4477</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>2.4477</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8128</v>
+        <v>1.676</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3081</v>
+        <v>0.0078</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5047</v>
+        <v>1.6683</v>
       </c>
       <c r="G8" t="n">
         <v>1.291</v>
@@ -1078,13 +1078,13 @@
         <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0603</v>
+        <v>-0.1971</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0617</v>
+        <v>-0.2386</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.122</v>
+        <v>0.0415</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5553</v>
+        <v>-0.4463</v>
       </c>
       <c r="E9" t="n">
         <v>0.2918</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8471</v>
+        <v>-0.7381</v>
       </c>
       <c r="G9" t="n">
         <v>0.1302</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5094</v>
+        <v>-0.4004</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0249</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5642</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0372</v>
+        <v>-0.9554</v>
       </c>
       <c r="E10" t="n">
         <v>0.1616</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1988</v>
+        <v>-1.117</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0288</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4547</v>
+        <v>-0.3729</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2839</v>
+        <v>-0.9658</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8373</v>
+        <v>-1.7372</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5534</v>
+        <v>0.7714</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6049</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.485</v>
+        <v>-0.1668</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1216</v>
+        <v>0.0965</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8556</v>
+        <v>-1.6916</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2211</v>
+        <v>-1.9208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3655</v>
+        <v>0.2292</v>
       </c>
       <c r="G12" t="n">
         <v>0.0423</v>
@@ -1390,13 +1390,13 @@
         <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1021</v>
+        <v>0.2661</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1817</v>
+        <v>0.1186</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2838</v>
+        <v>0.1475</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9422</v>
+        <v>-4.0784</v>
       </c>
       <c r="E13" t="n">
         <v>-3.505</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4372</v>
+        <v>-0.5735</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9776</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3824</v>
+        <v>-0.5187</v>
       </c>
       <c r="T13" t="n">
         <v>-0.6662</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2838</v>
+        <v>0.1475</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6119</v>
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.47809999999999</v>
+        <v>28.478</v>
       </c>
       <c r="E14" t="n">
         <v>16.6889</v>
@@ -1519,13 +1519,13 @@
         <v>33.0615</v>
       </c>
       <c r="J14" t="n">
-        <v>24.4234</v>
+        <v>24.42340000000001</v>
       </c>
       <c r="K14" t="n">
         <v>-2.7434</v>
       </c>
       <c r="L14" t="n">
-        <v>27.16670000000001</v>
+        <v>27.1667</v>
       </c>
       <c r="M14" t="n">
         <v>3.6782</v>
@@ -1537,7 +1537,7 @@
         <v>5.8947</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9700000000000002</v>
+        <v>-0.97</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.6421</v>
@@ -1546,7 +1546,7 @@
         <v>10.6719</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2187</v>
+        <v>-3.2188</v>
       </c>
       <c r="T14" t="n">
         <v>-4.234100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6434</v>
+        <v>2.2163</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6734</v>
+        <v>4.5733</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0299</v>
+        <v>-2.357</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9549</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.2891</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.046</v>
+        <v>-0.1461</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7623</v>
+        <v>0.4352</v>
       </c>
       <c r="V15" t="n">
         <v>0.9418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9858</v>
+        <v>1.1245</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2386</v>
+        <v>2.9627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2527</v>
+        <v>-1.8383</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0702</v>
+        <v>0.872</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4271</v>
+        <v>5.0083</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3569</v>
+        <v>-4.1364</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7713</v>
+        <v>3.6981</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7713</v>
+        <v>4.4366</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.7385</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-2.8262</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6558</v>
+        <v>0.5718</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3569</v>
+        <v>-3.3979</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3336</v>
+        <v>0.0883</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4374</v>
+        <v>-0.3772</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8962</v>
+        <v>0.4655</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3693</v>
+        <v>0.6132</v>
       </c>
       <c r="E17" t="n">
-        <v>2.262</v>
+        <v>1.1385</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8928</v>
+        <v>-0.5253</v>
       </c>
       <c r="G17" t="n">
-        <v>0.872</v>
+        <v>1.0702</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0083</v>
+        <v>2.4271</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.1364</v>
+        <v>-1.3569</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6981</v>
+        <v>1.7713</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4366</v>
+        <v>1.7713</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7385</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8262</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5718</v>
+        <v>0.6558</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.3979</v>
+        <v>-1.3569</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7761</v>
+        <v>-0.194</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6669</v>
+        <v>0.9609</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0779</v>
+        <v>0.3373</v>
       </c>
       <c r="U17" t="n">
-        <v>0.411</v>
+        <v>0.6236</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>R. MARQUINA ROMERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,37 +1813,37 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3788</v>
+        <v>-1.5582</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8286</v>
+        <v>-1.2503</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5502</v>
+        <v>-0.3079</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7954</v>
+        <v>-2.189</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4385</v>
+        <v>-0.1648</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3569</v>
+        <v>-2.0243</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9608</v>
+        <v>-1.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9608</v>
+        <v>-0.6261</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8346</v>
+        <v>-0.8956</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5223</v>
+        <v>0.4614</v>
       </c>
       <c r="O18" t="n">
         <v>-1.3569</v>
@@ -1858,19 +1858,19 @@
         <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9405</v>
+        <v>0.4368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8501</v>
+        <v>0.0432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.3937</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3795</v>
+        <v>-1.9977</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3269</v>
+        <v>-1.5293</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7064</v>
+        <v>-0.4684</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3326</v>
+        <v>-2.7954</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1666</v>
+        <v>-1.4385</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4992</v>
+        <v>-1.3569</v>
       </c>
       <c r="J19" t="n">
-        <v>0.798</v>
+        <v>-1.9608</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7168</v>
+        <v>-1.9608</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1306</v>
+        <v>-0.8346</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4498</v>
+        <v>0.5223</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5804</v>
+        <v>-1.3569</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>1.353</v>
+        <v>0.3216</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4991</v>
+        <v>0.1494</v>
       </c>
       <c r="U19" t="n">
-        <v>0.854</v>
+        <v>0.1722</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.788</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MARQUINA ROMERO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4125</v>
+        <v>-2.0619</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0501</v>
+        <v>-0.2737</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3624</v>
+        <v>-1.7882</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.189</v>
+        <v>-1.3326</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1648</v>
+        <v>1.1666</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0243</v>
+        <v>-2.4992</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2935</v>
+        <v>0.798</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6261</v>
+        <v>0.7168</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6673</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8956</v>
+        <v>-2.1306</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4614</v>
+        <v>0.4498</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3569</v>
+        <v>-2.5804</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5825</v>
+        <v>0.6707</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2434</v>
+        <v>-0.1015</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3392</v>
+        <v>0.7722</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5477</v>
+        <v>-4.7201</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9771</v>
+        <v>-1.877</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5706</v>
+        <v>-2.8432</v>
       </c>
       <c r="G21" t="n">
         <v>-4.984</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6303</v>
+        <v>0.4579</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0011</v>
+        <v>0.1012</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6292</v>
+        <v>0.3567</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2384</v>
+        <v>-5.5293</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.5766</v>
+        <v>-5.2763</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.253</v>
       </c>
       <c r="G22" t="n">
         <v>-5.7881</v>
@@ -2170,13 +2170,13 @@
         <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9264</v>
+        <v>-0.2173</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8345</v>
+        <v>-0.5342</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.092</v>
+        <v>0.3169</v>
       </c>
       <c r="V22" t="n">
         <v>0.2821</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6729</v>
+        <v>-7.0728</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4678</v>
+        <v>-5.1675</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2051</v>
+        <v>-1.9053</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2734</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4294</v>
+        <v>0.1707</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6651</v>
+        <v>-0.3648</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2358</v>
+        <v>0.5356</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.8468</v>
+        <v>-9.492000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3899</v>
+        <v>-5.0896</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.457</v>
+        <v>-4.4025</v>
       </c>
       <c r="G24" t="n">
         <v>-6.7261</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3147</v>
+        <v>0.0401</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4229</v>
+        <v>-0.1226</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8358</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-28.4781</v>
+        <v>-28.478</v>
       </c>
       <c r="E25" t="n">
         <v>-11.7892</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.6889</v>
+        <v>-16.6891</v>
       </c>
       <c r="G25" t="n">
         <v>-28.1013</v>
@@ -2389,7 +2389,7 @@
         <v>-24.4232</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7434</v>
+        <v>2.743399999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-27.1666</v>
@@ -2404,7 +2404,7 @@
         <v>11.6419</v>
       </c>
       <c r="S25" t="n">
-        <v>3.218699999999999</v>
+        <v>3.2188</v>
       </c>
       <c r="T25" t="n">
         <v>-1.0153</v>
